--- a/SubRES_TMPL/SubRES_Hydrogenupd.xlsx
+++ b/SubRES_TMPL/SubRES_Hydrogenupd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ee46c55b5fc2ded/Documents/Git/times-ireland-model/SubRES_TMPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{43F8AF59-5405-4C58-9FB4-9E762FAFDD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF0A3096-E47E-42A5-85BF-E57B3C32C4D2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{72794747-6911-46A7-A257-90AFB144FA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
     <sheet name="Regions" sheetId="15" r:id="rId2"/>
     <sheet name="config" sheetId="20" r:id="rId3"/>
-    <sheet name="FF2price" sheetId="23" r:id="rId4"/>
+    <sheet name="H2price" sheetId="23" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="__123Graph_AEUMILKPN" localSheetId="0" hidden="1">#REF!</definedName>
